--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X194"/>
+  <dimension ref="A1:X195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15598,6 +15598,84 @@
         <v>313.96</v>
       </c>
       <c r="X194" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>267.18</v>
+      </c>
+      <c r="C195" t="n">
+        <v>262.22</v>
+      </c>
+      <c r="D195" t="n">
+        <v>260.87</v>
+      </c>
+      <c r="E195" t="n">
+        <v>266.54</v>
+      </c>
+      <c r="F195" t="n">
+        <v>276.67</v>
+      </c>
+      <c r="G195" t="n">
+        <v>282.95</v>
+      </c>
+      <c r="H195" t="n">
+        <v>290.97</v>
+      </c>
+      <c r="I195" t="n">
+        <v>287.98</v>
+      </c>
+      <c r="J195" t="n">
+        <v>297.97</v>
+      </c>
+      <c r="K195" t="n">
+        <v>304.05</v>
+      </c>
+      <c r="L195" t="n">
+        <v>306.92</v>
+      </c>
+      <c r="M195" t="n">
+        <v>300.19</v>
+      </c>
+      <c r="N195" t="n">
+        <v>298.11</v>
+      </c>
+      <c r="O195" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="P195" t="n">
+        <v>301.03</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>303.03</v>
+      </c>
+      <c r="R195" t="n">
+        <v>294.14</v>
+      </c>
+      <c r="S195" t="n">
+        <v>306.77</v>
+      </c>
+      <c r="T195" t="n">
+        <v>323.92</v>
+      </c>
+      <c r="U195" t="n">
+        <v>348.36</v>
+      </c>
+      <c r="V195" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="W195" t="n">
+        <v>314.47</v>
+      </c>
+      <c r="X195" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15614,7 +15692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B195"/>
+  <dimension ref="A1:B196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17567,6 +17645,16 @@
       </c>
       <c r="B195" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>
@@ -17735,28 +17823,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.035106591682489</v>
+        <v>-1.035154291758774</v>
       </c>
       <c r="J2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K2" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2217224813030403</v>
+        <v>0.2235817059096805</v>
       </c>
       <c r="M2" t="n">
-        <v>12.55581237482932</v>
+        <v>12.49133966724088</v>
       </c>
       <c r="N2" t="n">
-        <v>233.1978577128945</v>
+        <v>231.9958201489104</v>
       </c>
       <c r="O2" t="n">
-        <v>15.27081719204622</v>
+        <v>15.23140900077568</v>
       </c>
       <c r="P2" t="n">
-        <v>294.3275790015908</v>
+        <v>294.3280255437799</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17813,28 +17901,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8093827001629395</v>
+        <v>-0.8121201108528265</v>
       </c>
       <c r="J3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K3" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1845298574073621</v>
+        <v>0.1871258370177719</v>
       </c>
       <c r="M3" t="n">
-        <v>11.045007415719</v>
+        <v>11.00213368625502</v>
       </c>
       <c r="N3" t="n">
-        <v>179.5059737085166</v>
+        <v>178.6243190666283</v>
       </c>
       <c r="O3" t="n">
-        <v>13.39798394194129</v>
+        <v>13.36504093022645</v>
       </c>
       <c r="P3" t="n">
-        <v>286.3338958180685</v>
+        <v>286.3595219691592</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17891,28 +17979,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7689434145894831</v>
+        <v>-0.7705648140048927</v>
       </c>
       <c r="J4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2089252215429951</v>
+        <v>0.2113738332204095</v>
       </c>
       <c r="M4" t="n">
-        <v>9.580143672476307</v>
+        <v>9.538509214677518</v>
       </c>
       <c r="N4" t="n">
-        <v>138.8177762912605</v>
+        <v>138.117528937567</v>
       </c>
       <c r="O4" t="n">
-        <v>11.78209558148551</v>
+        <v>11.75234142362989</v>
       </c>
       <c r="P4" t="n">
-        <v>282.7332037780296</v>
+        <v>282.7483824381229</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17969,28 +18057,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5465559224005713</v>
+        <v>-0.5462514540175604</v>
       </c>
       <c r="J5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1321335639320297</v>
+        <v>0.1332303791592274</v>
       </c>
       <c r="M5" t="n">
-        <v>8.69002850754427</v>
+        <v>8.647135707080226</v>
       </c>
       <c r="N5" t="n">
-        <v>121.6574209428028</v>
+        <v>121.0308606292075</v>
       </c>
       <c r="O5" t="n">
-        <v>11.02984229002404</v>
+        <v>11.00140266644247</v>
       </c>
       <c r="P5" t="n">
-        <v>280.5193002534185</v>
+        <v>280.5164499858959</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18047,28 +18135,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4449408334336503</v>
+        <v>-0.4397019675920269</v>
       </c>
       <c r="J6" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1018273782361094</v>
+        <v>0.1005069815138244</v>
       </c>
       <c r="M6" t="n">
-        <v>8.322772147657167</v>
+        <v>8.309541666299111</v>
       </c>
       <c r="N6" t="n">
-        <v>108.2753088137962</v>
+        <v>107.8770040162683</v>
       </c>
       <c r="O6" t="n">
-        <v>10.40554221623247</v>
+        <v>10.3863855125962</v>
       </c>
       <c r="P6" t="n">
-        <v>282.7001302165534</v>
+        <v>282.6510868018778</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18125,28 +18213,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3678180331968084</v>
+        <v>-0.3625233346633745</v>
       </c>
       <c r="J7" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K7" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08337120753967719</v>
+        <v>0.08184597632789781</v>
       </c>
       <c r="M7" t="n">
-        <v>7.802028719576262</v>
+        <v>7.794272498165114</v>
       </c>
       <c r="N7" t="n">
-        <v>92.23018741328937</v>
+        <v>91.91801401138765</v>
       </c>
       <c r="O7" t="n">
-        <v>9.603654898698171</v>
+        <v>9.587388278952076</v>
       </c>
       <c r="P7" t="n">
-        <v>286.9061606938087</v>
+        <v>286.8565946038175</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18203,28 +18291,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3614508314135395</v>
+        <v>-0.3574357767056849</v>
       </c>
       <c r="J8" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07896932015699121</v>
+        <v>0.07805134241790013</v>
       </c>
       <c r="M8" t="n">
-        <v>7.792654486132697</v>
+        <v>7.776418889996461</v>
       </c>
       <c r="N8" t="n">
-        <v>94.48085316912416</v>
+        <v>94.08770847404365</v>
       </c>
       <c r="O8" t="n">
-        <v>9.72012619100823</v>
+        <v>9.699881879386142</v>
       </c>
       <c r="P8" t="n">
-        <v>296.1281558684156</v>
+        <v>296.0905691084306</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18281,28 +18369,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4342886675731431</v>
+        <v>-0.4388139512186629</v>
       </c>
       <c r="J9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1077869715941904</v>
+        <v>0.1107204230680282</v>
       </c>
       <c r="M9" t="n">
-        <v>7.87639658060909</v>
+        <v>7.856563549568897</v>
       </c>
       <c r="N9" t="n">
-        <v>96.80302682186979</v>
+        <v>96.42328587709913</v>
       </c>
       <c r="O9" t="n">
-        <v>9.838852922057011</v>
+        <v>9.819535929823727</v>
       </c>
       <c r="P9" t="n">
-        <v>304.1982393883578</v>
+        <v>304.2406026343467</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18359,28 +18447,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3748401346914698</v>
+        <v>-0.3791979222301746</v>
       </c>
       <c r="J10" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K10" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08795372441509053</v>
+        <v>0.09059906765194392</v>
       </c>
       <c r="M10" t="n">
-        <v>7.610114570453972</v>
+        <v>7.588279011556676</v>
       </c>
       <c r="N10" t="n">
-        <v>90.34091039593282</v>
+        <v>89.98581546221916</v>
       </c>
       <c r="O10" t="n">
-        <v>9.504783553344749</v>
+        <v>9.486085360264221</v>
       </c>
       <c r="P10" t="n">
-        <v>312.4483605898957</v>
+        <v>312.489155828367</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18437,28 +18525,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.369219214208076</v>
+        <v>-0.3752307187487775</v>
       </c>
       <c r="J11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09372674887106613</v>
+        <v>0.09721225066697592</v>
       </c>
       <c r="M11" t="n">
-        <v>7.056911206334566</v>
+        <v>7.046570798314178</v>
       </c>
       <c r="N11" t="n">
-        <v>81.73232418861389</v>
+        <v>81.52145482891154</v>
       </c>
       <c r="O11" t="n">
-        <v>9.040593132566794</v>
+        <v>9.028923237513515</v>
       </c>
       <c r="P11" t="n">
-        <v>320.1506302509108</v>
+        <v>320.2069066891565</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18515,28 +18603,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3731681882733552</v>
+        <v>-0.3828439988202772</v>
       </c>
       <c r="J12" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K12" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08630783543623877</v>
+        <v>0.09081670804602371</v>
       </c>
       <c r="M12" t="n">
-        <v>7.42005986997563</v>
+        <v>7.427481544237061</v>
       </c>
       <c r="N12" t="n">
-        <v>91.4089154988103</v>
+        <v>91.48288882954223</v>
       </c>
       <c r="O12" t="n">
-        <v>9.560800986256869</v>
+        <v>9.564668777827189</v>
       </c>
       <c r="P12" t="n">
-        <v>327.0561968082279</v>
+        <v>327.1467764877465</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18593,28 +18681,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2002248803015679</v>
+        <v>-0.2138598230288948</v>
       </c>
       <c r="J13" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K13" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02229473087719636</v>
+        <v>0.02537270310121087</v>
       </c>
       <c r="M13" t="n">
-        <v>8.119371604881199</v>
+        <v>8.133722936375646</v>
       </c>
       <c r="N13" t="n">
-        <v>109.0112850782918</v>
+        <v>109.5319277450748</v>
       </c>
       <c r="O13" t="n">
-        <v>10.44084695215344</v>
+        <v>10.46575022370947</v>
       </c>
       <c r="P13" t="n">
-        <v>320.0409888051096</v>
+        <v>320.1686317283051</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -18671,28 +18759,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1741101378402868</v>
+        <v>-0.1851554489155999</v>
       </c>
       <c r="J14" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K14" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01661084750489505</v>
+        <v>0.01882287505333002</v>
       </c>
       <c r="M14" t="n">
-        <v>8.347122731316828</v>
+        <v>8.349374462904031</v>
       </c>
       <c r="N14" t="n">
-        <v>111.2785334335366</v>
+        <v>111.4153276575691</v>
       </c>
       <c r="O14" t="n">
-        <v>10.54886408261746</v>
+        <v>10.55534592789687</v>
       </c>
       <c r="P14" t="n">
-        <v>314.499881549031</v>
+        <v>314.6032817481702</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -18749,28 +18837,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1217400230985238</v>
+        <v>-0.129890240572111</v>
       </c>
       <c r="J15" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K15" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L15" t="n">
-        <v>0.008581342408012227</v>
+        <v>0.009825035082584033</v>
       </c>
       <c r="M15" t="n">
-        <v>8.026357269631939</v>
+        <v>8.013577802107573</v>
       </c>
       <c r="N15" t="n">
-        <v>106.1691324338685</v>
+        <v>106.0086651844536</v>
       </c>
       <c r="O15" t="n">
-        <v>10.3038406642314</v>
+        <v>10.29605095094491</v>
       </c>
       <c r="P15" t="n">
-        <v>311.3165534445548</v>
+        <v>311.3928513508836</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -18827,28 +18915,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1484656533059674</v>
+        <v>-0.1564167300404007</v>
       </c>
       <c r="J16" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K16" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01158134731119687</v>
+        <v>0.01293387147087866</v>
       </c>
       <c r="M16" t="n">
-        <v>8.310698943614151</v>
+        <v>8.298001362057017</v>
       </c>
       <c r="N16" t="n">
-        <v>116.6442906994221</v>
+        <v>116.4111569066272</v>
       </c>
       <c r="O16" t="n">
-        <v>10.80019864166498</v>
+        <v>10.78940021069879</v>
       </c>
       <c r="P16" t="n">
-        <v>313.4338394970917</v>
+        <v>313.5082731560539</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -18905,28 +18993,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1420286753589901</v>
+        <v>-0.1505602584728391</v>
       </c>
       <c r="J17" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K17" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01198410892451984</v>
+        <v>0.01353403278438792</v>
       </c>
       <c r="M17" t="n">
-        <v>8.025108407390785</v>
+        <v>8.01633684210147</v>
       </c>
       <c r="N17" t="n">
-        <v>103.1192884775994</v>
+        <v>103.0115869732757</v>
       </c>
       <c r="O17" t="n">
-        <v>10.15476678597787</v>
+        <v>10.14946239823941</v>
       </c>
       <c r="P17" t="n">
-        <v>315.887250551945</v>
+        <v>315.967118596125</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -18983,28 +19071,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.135982932506314</v>
+        <v>-0.1485727094560524</v>
       </c>
       <c r="J18" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K18" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L18" t="n">
-        <v>0.007274914978636637</v>
+        <v>0.008712951872402286</v>
       </c>
       <c r="M18" t="n">
-        <v>10.11155747226141</v>
+        <v>10.1074249897986</v>
       </c>
       <c r="N18" t="n">
-        <v>156.4586331090454</v>
+        <v>156.5750992123207</v>
       </c>
       <c r="O18" t="n">
-        <v>12.50834254044257</v>
+        <v>12.51299721139267</v>
       </c>
       <c r="P18" t="n">
-        <v>311.1840188853213</v>
+        <v>311.3018775345567</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19061,28 +19149,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1880736582514655</v>
+        <v>-0.1948870895792034</v>
       </c>
       <c r="J19" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K19" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01652986061484407</v>
+        <v>0.01787745769273053</v>
       </c>
       <c r="M19" t="n">
-        <v>8.946943745500439</v>
+        <v>8.93243255871039</v>
       </c>
       <c r="N19" t="n">
-        <v>130.4901058943366</v>
+        <v>130.0877949427166</v>
       </c>
       <c r="O19" t="n">
-        <v>11.42322659734703</v>
+        <v>11.40560366410812</v>
       </c>
       <c r="P19" t="n">
-        <v>318.988033718029</v>
+        <v>319.0518173590062</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19139,28 +19227,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.263818683163669</v>
+        <v>-0.2680407745184013</v>
       </c>
       <c r="J20" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K20" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03972346712940455</v>
+        <v>0.04133331410695618</v>
       </c>
       <c r="M20" t="n">
-        <v>7.675284997458964</v>
+        <v>7.653632998206699</v>
       </c>
       <c r="N20" t="n">
-        <v>104.3253660830964</v>
+        <v>103.8914069032712</v>
       </c>
       <c r="O20" t="n">
-        <v>10.21397895450624</v>
+        <v>10.19271342201237</v>
       </c>
       <c r="P20" t="n">
-        <v>335.3457423167811</v>
+        <v>335.3852672413293</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19217,28 +19305,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3466748935578282</v>
+        <v>-0.3513613807491245</v>
       </c>
       <c r="J21" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K21" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07704778296313486</v>
+        <v>0.07966032882965124</v>
       </c>
       <c r="M21" t="n">
-        <v>7.236392337334981</v>
+        <v>7.22680087452472</v>
       </c>
       <c r="N21" t="n">
-        <v>86.9607808674688</v>
+        <v>86.63128052441976</v>
       </c>
       <c r="O21" t="n">
-        <v>9.325276449921944</v>
+        <v>9.307592627764699</v>
       </c>
       <c r="P21" t="n">
-        <v>362.3357772655274</v>
+        <v>362.3806867676451</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19295,28 +19383,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1010424609234802</v>
+        <v>-0.1078485312360434</v>
       </c>
       <c r="J22" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K22" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L22" t="n">
-        <v>0.008238901645079899</v>
+        <v>0.009441603437183477</v>
       </c>
       <c r="M22" t="n">
-        <v>6.784529693911849</v>
+        <v>6.781427798584518</v>
       </c>
       <c r="N22" t="n">
-        <v>76.2035552143568</v>
+        <v>76.08048807208917</v>
       </c>
       <c r="O22" t="n">
-        <v>8.729464772502196</v>
+        <v>8.722412973030409</v>
       </c>
       <c r="P22" t="n">
-        <v>385.374706113785</v>
+        <v>385.4384208449388</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -19373,28 +19461,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1611521197072048</v>
+        <v>-0.1669036784632879</v>
       </c>
       <c r="J23" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K23" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02085024956183579</v>
+        <v>0.02250865353460318</v>
       </c>
       <c r="M23" t="n">
-        <v>6.824726923728712</v>
+        <v>6.824451588734503</v>
       </c>
       <c r="N23" t="n">
-        <v>75.6205022088119</v>
+        <v>75.423331873999</v>
       </c>
       <c r="O23" t="n">
-        <v>8.696004956806998</v>
+        <v>8.684660723021885</v>
       </c>
       <c r="P23" t="n">
-        <v>324.8483182096695</v>
+        <v>324.9021611767607</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -19432,7 +19520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X194"/>
+  <dimension ref="A1:X195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43095,6 +43183,128 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-34.42697031329449,172.93655766016494</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>-34.42700131731843,172.93745680368997</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>-34.426999770677234,172.9383552346394</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-34.42693492608815,172.93925227844437</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-34.42682986657595,172.94014843987063</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-34.42675952175557,172.9410453613635</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-34.42667291427329,172.9419638524201</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-34.42664440653606,172.94288599490835</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-34.426496519134616,172.94377517765378</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-34.42638391743491,172.94466558436972</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-34.42630017631901,172.9455587143082</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>-34.426302747156086,172.9464599909202</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-34.42626351055818,172.94735732185856</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>-34.426193974832316,172.94825179268977</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>-34.42612138219794,172.94914597475974</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>-34.42604546293445,172.95003984253918</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>-34.42606745357799,172.95094295520727</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>-34.425894470516184,172.95184734249165</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>-34.425632842595405,172.95274882108833</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>-34.42523986015934,172.95357994422042</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>-34.424827437926055,172.95438312676842</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>-34.425186562455174,172.95541287401693</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X195"/>
+  <dimension ref="A1:X197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15676,6 +15676,162 @@
         <v>314.47</v>
       </c>
       <c r="X195" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>264.62</v>
+      </c>
+      <c r="C196" t="n">
+        <v>264.19</v>
+      </c>
+      <c r="D196" t="n">
+        <v>264.62</v>
+      </c>
+      <c r="E196" t="n">
+        <v>270.69</v>
+      </c>
+      <c r="F196" t="n">
+        <v>277.59</v>
+      </c>
+      <c r="G196" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="H196" t="n">
+        <v>291.76</v>
+      </c>
+      <c r="I196" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="J196" t="n">
+        <v>301.29</v>
+      </c>
+      <c r="K196" t="n">
+        <v>308.12</v>
+      </c>
+      <c r="L196" t="n">
+        <v>308.84</v>
+      </c>
+      <c r="M196" t="n">
+        <v>301.89</v>
+      </c>
+      <c r="N196" t="n">
+        <v>298.36</v>
+      </c>
+      <c r="O196" t="n">
+        <v>299.62</v>
+      </c>
+      <c r="P196" t="n">
+        <v>302.08</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>305.53</v>
+      </c>
+      <c r="R196" t="n">
+        <v>299.31</v>
+      </c>
+      <c r="S196" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="T196" t="n">
+        <v>327.24</v>
+      </c>
+      <c r="U196" t="n">
+        <v>352.43</v>
+      </c>
+      <c r="V196" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="W196" t="n">
+        <v>313.66</v>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>267.84</v>
+      </c>
+      <c r="C197" t="n">
+        <v>266.91</v>
+      </c>
+      <c r="D197" t="n">
+        <v>267.51</v>
+      </c>
+      <c r="E197" t="n">
+        <v>273</v>
+      </c>
+      <c r="F197" t="n">
+        <v>279.22</v>
+      </c>
+      <c r="G197" t="n">
+        <v>286.29</v>
+      </c>
+      <c r="H197" t="n">
+        <v>293.59</v>
+      </c>
+      <c r="I197" t="n">
+        <v>293.19</v>
+      </c>
+      <c r="J197" t="n">
+        <v>303.71</v>
+      </c>
+      <c r="K197" t="n">
+        <v>310.26</v>
+      </c>
+      <c r="L197" t="n">
+        <v>311.29</v>
+      </c>
+      <c r="M197" t="n">
+        <v>304.25</v>
+      </c>
+      <c r="N197" t="n">
+        <v>300.02</v>
+      </c>
+      <c r="O197" t="n">
+        <v>300.58</v>
+      </c>
+      <c r="P197" t="n">
+        <v>303.32</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>307.16</v>
+      </c>
+      <c r="R197" t="n">
+        <v>301.92</v>
+      </c>
+      <c r="S197" t="n">
+        <v>309.57</v>
+      </c>
+      <c r="T197" t="n">
+        <v>328.28</v>
+      </c>
+      <c r="U197" t="n">
+        <v>353.95</v>
+      </c>
+      <c r="V197" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="W197" t="n">
+        <v>316.52</v>
+      </c>
+      <c r="X197" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -15692,7 +15848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B196"/>
+  <dimension ref="A1:B198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17655,6 +17811,26 @@
       </c>
       <c r="B196" t="n">
         <v>1.08</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -17823,28 +17999,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.035154291758774</v>
+        <v>-1.036830073708237</v>
       </c>
       <c r="J2" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K2" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2235817059096805</v>
+        <v>0.2277770140149463</v>
       </c>
       <c r="M2" t="n">
-        <v>12.49133966724088</v>
+        <v>12.37988895723875</v>
       </c>
       <c r="N2" t="n">
-        <v>231.9958201489104</v>
+        <v>229.6637519301378</v>
       </c>
       <c r="O2" t="n">
-        <v>15.23140900077568</v>
+        <v>15.1546610628591</v>
       </c>
       <c r="P2" t="n">
-        <v>294.3280255437799</v>
+        <v>294.3437596042979</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17901,28 +18077,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8121201108528265</v>
+        <v>-0.8111829423186012</v>
       </c>
       <c r="J3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1871258370177719</v>
+        <v>0.1899553200845795</v>
       </c>
       <c r="M3" t="n">
-        <v>11.00213368625502</v>
+        <v>10.9041916551979</v>
       </c>
       <c r="N3" t="n">
-        <v>178.6243190666283</v>
+        <v>176.823338908979</v>
       </c>
       <c r="O3" t="n">
-        <v>13.36504093022645</v>
+        <v>13.29749370779994</v>
       </c>
       <c r="P3" t="n">
-        <v>286.3595219691592</v>
+        <v>286.3507002112238</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17979,28 +18155,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7705648140048927</v>
+        <v>-0.7641027745109416</v>
       </c>
       <c r="J4" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K4" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2113738332204095</v>
+        <v>0.2118771101606566</v>
       </c>
       <c r="M4" t="n">
-        <v>9.538509214677518</v>
+        <v>9.481355741491971</v>
       </c>
       <c r="N4" t="n">
-        <v>138.117528937567</v>
+        <v>136.8541301013933</v>
       </c>
       <c r="O4" t="n">
-        <v>11.75234142362989</v>
+        <v>11.69846699791871</v>
       </c>
       <c r="P4" t="n">
-        <v>282.7483824381229</v>
+        <v>282.6876332175349</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18057,28 +18233,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5462514540175604</v>
+        <v>-0.535917114956343</v>
       </c>
       <c r="J5" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K5" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1332303791592274</v>
+        <v>0.1309331512675795</v>
       </c>
       <c r="M5" t="n">
-        <v>8.647135707080226</v>
+        <v>8.622358239871618</v>
       </c>
       <c r="N5" t="n">
-        <v>121.0308606292075</v>
+        <v>120.1277303594776</v>
       </c>
       <c r="O5" t="n">
-        <v>11.00140266644247</v>
+        <v>10.96027966611608</v>
       </c>
       <c r="P5" t="n">
-        <v>280.5164499858959</v>
+        <v>280.419309116561</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18135,28 +18311,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4397019675920269</v>
+        <v>-0.4264098199951449</v>
       </c>
       <c r="J6" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K6" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1005069815138244</v>
+        <v>0.09647226714761148</v>
       </c>
       <c r="M6" t="n">
-        <v>8.309541666299111</v>
+        <v>8.299212613064318</v>
       </c>
       <c r="N6" t="n">
-        <v>107.8770040162683</v>
+        <v>107.3094213178465</v>
       </c>
       <c r="O6" t="n">
-        <v>10.3863855125962</v>
+        <v>10.35902607960065</v>
       </c>
       <c r="P6" t="n">
-        <v>282.6510868018778</v>
+        <v>282.5261497883513</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18213,28 +18389,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3625233346633745</v>
+        <v>-0.3483502992020459</v>
       </c>
       <c r="J7" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K7" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08184597632789781</v>
+        <v>0.0770535720658384</v>
       </c>
       <c r="M7" t="n">
-        <v>7.794272498165114</v>
+        <v>7.800187614808984</v>
       </c>
       <c r="N7" t="n">
-        <v>91.91801401138765</v>
+        <v>91.59263375396623</v>
       </c>
       <c r="O7" t="n">
-        <v>9.587388278952076</v>
+        <v>9.570404053850925</v>
       </c>
       <c r="P7" t="n">
-        <v>286.8565946038175</v>
+        <v>286.7233748203179</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18291,28 +18467,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3574357767056849</v>
+        <v>-0.3465587274182449</v>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K8" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07805134241790013</v>
+        <v>0.07489138779985061</v>
       </c>
       <c r="M8" t="n">
-        <v>7.776418889996461</v>
+        <v>7.760818780893628</v>
       </c>
       <c r="N8" t="n">
-        <v>94.08770847404365</v>
+        <v>93.48866987037873</v>
       </c>
       <c r="O8" t="n">
-        <v>9.699881879386142</v>
+        <v>9.668953918101934</v>
       </c>
       <c r="P8" t="n">
-        <v>296.0905691084306</v>
+        <v>295.9883298862215</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18369,28 +18545,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4388139512186629</v>
+        <v>-0.4397247732661273</v>
       </c>
       <c r="J9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1107204230680282</v>
+        <v>0.1132005836687845</v>
       </c>
       <c r="M9" t="n">
-        <v>7.856563549568897</v>
+        <v>7.785510073414523</v>
       </c>
       <c r="N9" t="n">
-        <v>96.42328587709913</v>
+        <v>95.45156529284576</v>
       </c>
       <c r="O9" t="n">
-        <v>9.819535929823727</v>
+        <v>9.76993169335619</v>
       </c>
       <c r="P9" t="n">
-        <v>304.2406026343467</v>
+        <v>304.2491534874741</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18447,28 +18623,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3791979222301746</v>
+        <v>-0.3792590824501075</v>
       </c>
       <c r="J10" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K10" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09059906765194392</v>
+        <v>0.0923510262031948</v>
       </c>
       <c r="M10" t="n">
-        <v>7.588279011556676</v>
+        <v>7.523114389523311</v>
       </c>
       <c r="N10" t="n">
-        <v>89.98581546221916</v>
+        <v>89.08254794168796</v>
       </c>
       <c r="O10" t="n">
-        <v>9.486085360264221</v>
+        <v>9.43835515022019</v>
       </c>
       <c r="P10" t="n">
-        <v>312.489155828367</v>
+        <v>312.4897186352579</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18525,28 +18701,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3752307187487775</v>
+        <v>-0.3773500542501936</v>
       </c>
       <c r="J11" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K11" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09721225066697592</v>
+        <v>0.1000461329213077</v>
       </c>
       <c r="M11" t="n">
-        <v>7.046570798314178</v>
+        <v>6.983687288814191</v>
       </c>
       <c r="N11" t="n">
-        <v>81.52145482891154</v>
+        <v>80.71481010895248</v>
       </c>
       <c r="O11" t="n">
-        <v>9.028923237513515</v>
+        <v>8.984142146524201</v>
       </c>
       <c r="P11" t="n">
-        <v>320.2069066891565</v>
+        <v>320.2268150038175</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18603,28 +18779,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3828439988202772</v>
+        <v>-0.3956576649190811</v>
       </c>
       <c r="J12" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K12" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09081670804602371</v>
+        <v>0.09774875684000961</v>
       </c>
       <c r="M12" t="n">
-        <v>7.427481544237061</v>
+        <v>7.411126663817052</v>
       </c>
       <c r="N12" t="n">
-        <v>91.48288882954223</v>
+        <v>91.05417596410389</v>
       </c>
       <c r="O12" t="n">
-        <v>9.564668777827189</v>
+        <v>9.542231183748584</v>
       </c>
       <c r="P12" t="n">
-        <v>327.1467764877465</v>
+        <v>327.2671960837548</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18681,28 +18857,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2138598230288948</v>
+        <v>-0.2347775142684869</v>
       </c>
       <c r="J13" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K13" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02537270310121087</v>
+        <v>0.03068231018152456</v>
       </c>
       <c r="M13" t="n">
-        <v>8.133722936375646</v>
+        <v>8.138552187883157</v>
       </c>
       <c r="N13" t="n">
-        <v>109.5319277450748</v>
+        <v>109.7325667146739</v>
       </c>
       <c r="O13" t="n">
-        <v>10.46575022370947</v>
+        <v>10.47533134152204</v>
       </c>
       <c r="P13" t="n">
-        <v>320.1686317283051</v>
+        <v>320.3652190723084</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -18759,28 +18935,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1851554489155999</v>
+        <v>-0.2043804368084594</v>
       </c>
       <c r="J14" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K14" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01882287505333002</v>
+        <v>0.02308578528996885</v>
       </c>
       <c r="M14" t="n">
-        <v>8.349374462904031</v>
+        <v>8.343168713478423</v>
       </c>
       <c r="N14" t="n">
-        <v>111.4153276575691</v>
+        <v>111.3870950172538</v>
       </c>
       <c r="O14" t="n">
-        <v>10.55534592789687</v>
+        <v>10.55400848101108</v>
       </c>
       <c r="P14" t="n">
-        <v>314.6032817481702</v>
+        <v>314.7839633026133</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -18837,28 +19013,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.129890240572111</v>
+        <v>-0.1442531485540066</v>
       </c>
       <c r="J15" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K15" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L15" t="n">
-        <v>0.009825035082584033</v>
+        <v>0.012271524138742</v>
       </c>
       <c r="M15" t="n">
-        <v>8.013577802107573</v>
+        <v>7.981281720402161</v>
       </c>
       <c r="N15" t="n">
-        <v>106.0086651844536</v>
+        <v>105.5441400295233</v>
       </c>
       <c r="O15" t="n">
-        <v>10.29605095094491</v>
+        <v>10.27346777040369</v>
       </c>
       <c r="P15" t="n">
-        <v>311.3928513508836</v>
+        <v>311.5278391723623</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -18915,28 +19091,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1564167300404007</v>
+        <v>-0.1686300344198615</v>
       </c>
       <c r="J16" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K16" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01293387147087866</v>
+        <v>0.0152549426577161</v>
       </c>
       <c r="M16" t="n">
-        <v>8.298001362057017</v>
+        <v>8.25879674450022</v>
       </c>
       <c r="N16" t="n">
-        <v>116.4111569066272</v>
+        <v>115.671812944039</v>
       </c>
       <c r="O16" t="n">
-        <v>10.78940021069879</v>
+        <v>10.75508312120548</v>
       </c>
       <c r="P16" t="n">
-        <v>313.5082731560539</v>
+        <v>313.6230561343985</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -18993,28 +19169,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1505602584728391</v>
+        <v>-0.1608875592887598</v>
       </c>
       <c r="J17" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K17" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01353403278438792</v>
+        <v>0.01569660101692327</v>
       </c>
       <c r="M17" t="n">
-        <v>8.01633684210147</v>
+        <v>7.973561747887579</v>
       </c>
       <c r="N17" t="n">
-        <v>103.0115869732757</v>
+        <v>102.2851878561904</v>
       </c>
       <c r="O17" t="n">
-        <v>10.14946239823941</v>
+        <v>10.11361398591969</v>
       </c>
       <c r="P17" t="n">
-        <v>315.967118596125</v>
+        <v>316.0641736485302</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -19071,28 +19247,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1485727094560524</v>
+        <v>-0.1609352472761107</v>
       </c>
       <c r="J18" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K18" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L18" t="n">
-        <v>0.008712951872402286</v>
+        <v>0.01039007923406798</v>
       </c>
       <c r="M18" t="n">
-        <v>10.1074249897986</v>
+        <v>10.05052817271272</v>
       </c>
       <c r="N18" t="n">
-        <v>156.5750992123207</v>
+        <v>155.450448410561</v>
       </c>
       <c r="O18" t="n">
-        <v>12.51299721139267</v>
+        <v>12.46797691730944</v>
       </c>
       <c r="P18" t="n">
-        <v>311.3018775345567</v>
+        <v>311.4180563027275</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19149,28 +19325,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1948870895792034</v>
+        <v>-0.2043640839443917</v>
       </c>
       <c r="J19" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K19" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01787745769273053</v>
+        <v>0.01998832648002591</v>
       </c>
       <c r="M19" t="n">
-        <v>8.93243255871039</v>
+        <v>8.884490421687898</v>
       </c>
       <c r="N19" t="n">
-        <v>130.0877949427166</v>
+        <v>129.0352641459046</v>
       </c>
       <c r="O19" t="n">
-        <v>11.40560366410812</v>
+        <v>11.35936900298184</v>
       </c>
       <c r="P19" t="n">
-        <v>319.0518173590062</v>
+        <v>319.1408804372212</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19227,28 +19403,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2680407745184013</v>
+        <v>-0.2691119510054168</v>
       </c>
       <c r="J20" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K20" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04133331410695618</v>
+        <v>0.04249144019523265</v>
       </c>
       <c r="M20" t="n">
-        <v>7.653632998206699</v>
+        <v>7.580001433609464</v>
       </c>
       <c r="N20" t="n">
-        <v>103.8914069032712</v>
+        <v>102.8375303304599</v>
       </c>
       <c r="O20" t="n">
-        <v>10.19271342201237</v>
+        <v>10.14088410004078</v>
       </c>
       <c r="P20" t="n">
-        <v>335.3852672413293</v>
+        <v>335.3953296893349</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19305,28 +19481,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3513613807491245</v>
+        <v>-0.3512985402076075</v>
       </c>
       <c r="J21" t="n">
+        <v>196</v>
+      </c>
+      <c r="K21" t="n">
         <v>194</v>
       </c>
-      <c r="K21" t="n">
-        <v>192</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.07966032882965124</v>
+        <v>0.0811907636847099</v>
       </c>
       <c r="M21" t="n">
-        <v>7.22680087452472</v>
+        <v>7.160106751937273</v>
       </c>
       <c r="N21" t="n">
-        <v>86.63128052441976</v>
+        <v>85.74415182598121</v>
       </c>
       <c r="O21" t="n">
-        <v>9.307592627764699</v>
+        <v>9.259813811626085</v>
       </c>
       <c r="P21" t="n">
-        <v>362.3806867676451</v>
+        <v>362.3800745002997</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19383,28 +19559,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1078485312360434</v>
+        <v>-0.1099590708108579</v>
       </c>
       <c r="J22" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K22" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009441603437183477</v>
+        <v>0.01001320502252978</v>
       </c>
       <c r="M22" t="n">
-        <v>6.781427798584518</v>
+        <v>6.721948848583915</v>
       </c>
       <c r="N22" t="n">
-        <v>76.08048807208917</v>
+        <v>75.32911595393566</v>
       </c>
       <c r="O22" t="n">
-        <v>8.722412973030409</v>
+        <v>8.679234756240648</v>
       </c>
       <c r="P22" t="n">
-        <v>385.4384208449388</v>
+        <v>385.4582465512374</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -19461,28 +19637,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1669036784632879</v>
+        <v>-0.1768024164482054</v>
       </c>
       <c r="J23" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K23" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02250865353460318</v>
+        <v>0.02560284338331087</v>
       </c>
       <c r="M23" t="n">
-        <v>6.824451588734503</v>
+        <v>6.814882138662006</v>
       </c>
       <c r="N23" t="n">
-        <v>75.423331873999</v>
+        <v>74.96674529250829</v>
       </c>
       <c r="O23" t="n">
-        <v>8.684660723021885</v>
+        <v>8.658333863539122</v>
       </c>
       <c r="P23" t="n">
-        <v>324.9021611767607</v>
+        <v>324.9951822105033</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -19520,7 +19696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X195"/>
+  <dimension ref="A1:X197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43305,6 +43481,250 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>-34.42699339631154,172.93655816560093</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>-34.426983554217145,172.93745641461825</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>-34.42696595767022,172.93835449378705</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-34.42689750636346,172.9392514583103</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-34.426821571119554,172.9401482580008</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-34.42675059512387,172.94104516559437</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-34.4266657972246,172.94196346066641</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-34.42661500077133,172.94288331004955</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-34.42646666954004,172.9437723607493</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-34.42634732472416,172.94466213087128</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>-34.426282913917305,172.94555708502216</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>-34.426287462744654,172.94645854821675</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>-34.42626126285158,172.9473571096808</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>-34.426191996851365,172.9482516059599</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>-34.426111941838265,172.94914508348495</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>-34.426022985897106,172.95003772030418</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>-34.42602097108543,172.95093856610086</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>-34.42588434069716,172.951846000562</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>-34.425603439300865,172.952742005821</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>-34.42520419630299,172.95356947185562</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>-34.42478415063984,172.95437041564756</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>-34.425193660155315,172.9554149583001</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>-34.426964362204146,172.93655752985725</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>-34.426959028513764,172.93745587742308</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>-34.4269398991127,172.93835392283722</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-34.42687667755275,172.93925100180226</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-34.426806873734826,172.940147935775</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-34.42672940564453,172.94104470088996</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-34.426649310896586,172.94196255318664</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-34.426597555149336,172.94288171719845</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-34.426444911702916,172.94377030746477</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-34.42632808433066,172.9446603150281</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-34.42626088637336,172.94555500598628</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-34.42626624438516,172.94645654540577</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-34.42624633807981,172.94735570082088</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>-34.426183365661714,172.9482507911388</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>-34.426100793223014,172.94914403093213</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>-34.4260083308687,172.95003633660755</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>-34.42599750506865,172.95093635032558</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>-34.42586937007959,172.95184401735685</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>-34.42559422863019,172.95273987091895</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>-34.42519087712294,172.95356556080273</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>-34.42476539865705,172.95436490921466</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>-34.425168599139816,172.95540759898077</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X197"/>
+  <dimension ref="A1:X198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15834,6 +15834,84 @@
       <c r="X197" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>278.36</v>
+      </c>
+      <c r="C198" t="n">
+        <v>275.57</v>
+      </c>
+      <c r="D198" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="E198" t="n">
+        <v>276.33</v>
+      </c>
+      <c r="F198" t="n">
+        <v>282.66</v>
+      </c>
+      <c r="G198" t="n">
+        <v>289.93</v>
+      </c>
+      <c r="H198" t="n">
+        <v>294.55</v>
+      </c>
+      <c r="I198" t="n">
+        <v>298.04</v>
+      </c>
+      <c r="J198" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="K198" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="L198" t="n">
+        <v>314.92</v>
+      </c>
+      <c r="M198" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="N198" t="n">
+        <v>304.76</v>
+      </c>
+      <c r="O198" t="n">
+        <v>301.74</v>
+      </c>
+      <c r="P198" t="n">
+        <v>302.62</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="R198" t="n">
+        <v>313.4</v>
+      </c>
+      <c r="S198" t="n">
+        <v>310.43</v>
+      </c>
+      <c r="T198" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="U198" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="V198" t="n">
+        <v>384.76</v>
+      </c>
+      <c r="W198" t="n">
+        <v>322.64</v>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B198"/>
+  <dimension ref="A1:B199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17831,6 +17909,16 @@
       </c>
       <c r="B198" t="n">
         <v>0.93</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -17999,28 +18087,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.036830073708237</v>
+        <v>-1.026210272101575</v>
       </c>
       <c r="J2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K2" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2277770140149463</v>
+        <v>0.2255305954773422</v>
       </c>
       <c r="M2" t="n">
-        <v>12.37988895723875</v>
+        <v>12.37891939442598</v>
       </c>
       <c r="N2" t="n">
-        <v>229.6637519301378</v>
+        <v>229.1633822140338</v>
       </c>
       <c r="O2" t="n">
-        <v>15.1546610628591</v>
+        <v>15.13814328819865</v>
       </c>
       <c r="P2" t="n">
-        <v>294.3437596042979</v>
+        <v>294.2424241190193</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18077,28 +18165,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8111829423186012</v>
+        <v>-0.8012892307015905</v>
       </c>
       <c r="J3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1899553200845795</v>
+        <v>0.1873322284724426</v>
       </c>
       <c r="M3" t="n">
-        <v>10.9041916551979</v>
+        <v>10.90635803715859</v>
       </c>
       <c r="N3" t="n">
-        <v>176.823338908979</v>
+        <v>176.5033118031297</v>
       </c>
       <c r="O3" t="n">
-        <v>13.29749370779994</v>
+        <v>13.28545489635676</v>
       </c>
       <c r="P3" t="n">
-        <v>286.3507002112238</v>
+        <v>286.256293168131</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18155,28 +18243,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7641027745109416</v>
+        <v>-0.7529287505765974</v>
       </c>
       <c r="J4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2118771101606566</v>
+        <v>0.2078680685053571</v>
       </c>
       <c r="M4" t="n">
-        <v>9.481355741491971</v>
+        <v>9.501000086435781</v>
       </c>
       <c r="N4" t="n">
-        <v>136.8541301013933</v>
+        <v>136.8961426405408</v>
       </c>
       <c r="O4" t="n">
-        <v>11.69846699791871</v>
+        <v>11.70026250306124</v>
       </c>
       <c r="P4" t="n">
-        <v>282.6876332175349</v>
+        <v>282.5810092729604</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18233,28 +18321,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.535917114956343</v>
+        <v>-0.526584636427015</v>
       </c>
       <c r="J5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1309331512675795</v>
+        <v>0.127697080775383</v>
       </c>
       <c r="M5" t="n">
-        <v>8.622358239871618</v>
+        <v>8.634306569990461</v>
       </c>
       <c r="N5" t="n">
-        <v>120.1277303594776</v>
+        <v>120.0318318534704</v>
       </c>
       <c r="O5" t="n">
-        <v>10.96027966611608</v>
+        <v>10.95590397244656</v>
       </c>
       <c r="P5" t="n">
-        <v>280.419309116561</v>
+        <v>280.3302574303196</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18311,28 +18399,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4264098199951449</v>
+        <v>-0.4158735117225523</v>
       </c>
       <c r="J6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09647226714761148</v>
+        <v>0.09258065655368075</v>
       </c>
       <c r="M6" t="n">
-        <v>8.299212613064318</v>
+        <v>8.315635187108914</v>
       </c>
       <c r="N6" t="n">
-        <v>107.3094213178465</v>
+        <v>107.41971733154</v>
       </c>
       <c r="O6" t="n">
-        <v>10.35902607960065</v>
+        <v>10.36434837949497</v>
       </c>
       <c r="P6" t="n">
-        <v>282.5261497883513</v>
+        <v>282.4256110069884</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18389,28 +18477,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3483502992020459</v>
+        <v>-0.3368858359412198</v>
       </c>
       <c r="J7" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K7" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0770535720658384</v>
+        <v>0.07257505528993469</v>
       </c>
       <c r="M7" t="n">
-        <v>7.800187614808984</v>
+        <v>7.827886352365412</v>
       </c>
       <c r="N7" t="n">
-        <v>91.59263375396623</v>
+        <v>91.90319513864679</v>
       </c>
       <c r="O7" t="n">
-        <v>9.570404053850925</v>
+        <v>9.586615416227293</v>
       </c>
       <c r="P7" t="n">
-        <v>286.7233748203179</v>
+        <v>286.6139794670877</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18467,28 +18555,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3465587274182449</v>
+        <v>-0.339414386077481</v>
       </c>
       <c r="J8" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K8" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07489138779985061</v>
+        <v>0.0725553577129382</v>
       </c>
       <c r="M8" t="n">
-        <v>7.760818780893628</v>
+        <v>7.762050441134829</v>
       </c>
       <c r="N8" t="n">
-        <v>93.48866987037873</v>
+        <v>93.31526856212071</v>
       </c>
       <c r="O8" t="n">
-        <v>9.668953918101934</v>
+        <v>9.659982844815032</v>
       </c>
       <c r="P8" t="n">
-        <v>295.9883298862215</v>
+        <v>295.9201576807909</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18545,28 +18633,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4397247732661273</v>
+        <v>-0.4346984943391409</v>
       </c>
       <c r="J9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1132005836687845</v>
+        <v>0.11181484123578</v>
       </c>
       <c r="M9" t="n">
-        <v>7.785510073414523</v>
+        <v>7.777778927752488</v>
       </c>
       <c r="N9" t="n">
-        <v>95.45156529284576</v>
+        <v>95.11610151140177</v>
       </c>
       <c r="O9" t="n">
-        <v>9.76993169335619</v>
+        <v>9.752748408084861</v>
       </c>
       <c r="P9" t="n">
-        <v>304.2491534874741</v>
+        <v>304.201192100522</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18623,28 +18711,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3792590824501075</v>
+        <v>-0.3730914183599735</v>
       </c>
       <c r="J10" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K10" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0923510262031948</v>
+        <v>0.0903063896470534</v>
       </c>
       <c r="M10" t="n">
-        <v>7.523114389523311</v>
+        <v>7.527678211670871</v>
       </c>
       <c r="N10" t="n">
-        <v>89.08254794168796</v>
+        <v>88.85479988259031</v>
       </c>
       <c r="O10" t="n">
-        <v>9.43835515022019</v>
+        <v>9.426282399896065</v>
       </c>
       <c r="P10" t="n">
-        <v>312.4897186352579</v>
+        <v>312.4308660072373</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18701,28 +18789,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3773500542501936</v>
+        <v>-0.3737349525355302</v>
       </c>
       <c r="J11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1000461329213077</v>
+        <v>0.0991913488664119</v>
       </c>
       <c r="M11" t="n">
-        <v>6.983687288814191</v>
+        <v>6.972693545166072</v>
       </c>
       <c r="N11" t="n">
-        <v>80.71481010895248</v>
+        <v>80.38220095493553</v>
       </c>
       <c r="O11" t="n">
-        <v>8.984142146524201</v>
+        <v>8.965612134981946</v>
       </c>
       <c r="P11" t="n">
-        <v>320.2268150038175</v>
+        <v>320.1923192476673</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18779,28 +18867,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3956576649190811</v>
+        <v>-0.3973509119850668</v>
       </c>
       <c r="J12" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K12" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09774875684000961</v>
+        <v>0.09944059205953415</v>
       </c>
       <c r="M12" t="n">
-        <v>7.411126663817052</v>
+        <v>7.38109755862357</v>
       </c>
       <c r="N12" t="n">
-        <v>91.05417596410389</v>
+        <v>90.60888867015441</v>
       </c>
       <c r="O12" t="n">
-        <v>9.542231183748584</v>
+        <v>9.518870136216504</v>
       </c>
       <c r="P12" t="n">
-        <v>327.2671960837548</v>
+        <v>327.2833532606479</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18857,28 +18945,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2347775142684869</v>
+        <v>-0.2369131984678494</v>
       </c>
       <c r="J13" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K13" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03068231018152456</v>
+        <v>0.03154279906264146</v>
       </c>
       <c r="M13" t="n">
-        <v>8.138552187883157</v>
+        <v>8.105996809147054</v>
       </c>
       <c r="N13" t="n">
-        <v>109.7325667146739</v>
+        <v>109.2024607127622</v>
       </c>
       <c r="O13" t="n">
-        <v>10.47533134152204</v>
+        <v>10.44999812022769</v>
       </c>
       <c r="P13" t="n">
-        <v>320.3652190723084</v>
+        <v>320.3855980400858</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -18935,28 +19023,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2043804368084594</v>
+        <v>-0.2086158264480809</v>
       </c>
       <c r="J14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02308578528996885</v>
+        <v>0.0242584858998246</v>
       </c>
       <c r="M14" t="n">
-        <v>8.343168713478423</v>
+        <v>8.317875536204616</v>
       </c>
       <c r="N14" t="n">
-        <v>111.3870950172538</v>
+        <v>110.9275208452598</v>
       </c>
       <c r="O14" t="n">
-        <v>10.55400848101108</v>
+        <v>10.53221348270437</v>
       </c>
       <c r="P14" t="n">
-        <v>314.7839633026133</v>
+        <v>314.8243779243145</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -19013,28 +19101,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1442531485540066</v>
+        <v>-0.1497401015463972</v>
       </c>
       <c r="J15" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K15" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L15" t="n">
-        <v>0.012271524138742</v>
+        <v>0.01332799239164806</v>
       </c>
       <c r="M15" t="n">
-        <v>7.981281720402161</v>
+        <v>7.958979646299882</v>
       </c>
       <c r="N15" t="n">
-        <v>105.5441400295233</v>
+        <v>105.1860210451894</v>
       </c>
       <c r="O15" t="n">
-        <v>10.27346777040369</v>
+        <v>10.2560236468716</v>
       </c>
       <c r="P15" t="n">
-        <v>311.5278391723623</v>
+        <v>311.5801963693024</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -19091,28 +19179,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1686300344198615</v>
+        <v>-0.174639783812994</v>
       </c>
       <c r="J16" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K16" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0152549426577161</v>
+        <v>0.01648616824732629</v>
       </c>
       <c r="M16" t="n">
-        <v>8.25879674450022</v>
+        <v>8.238705795454331</v>
       </c>
       <c r="N16" t="n">
-        <v>115.671812944039</v>
+        <v>115.2977477772608</v>
       </c>
       <c r="O16" t="n">
-        <v>10.75508312120548</v>
+        <v>10.73767888220079</v>
       </c>
       <c r="P16" t="n">
-        <v>313.6230561343985</v>
+        <v>313.6804019204793</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -19169,28 +19257,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1608875592887598</v>
+        <v>-0.1644518859493033</v>
       </c>
       <c r="J17" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K17" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01569660101692327</v>
+        <v>0.01654937567996928</v>
       </c>
       <c r="M17" t="n">
-        <v>7.973561747887579</v>
+        <v>7.946546868698226</v>
       </c>
       <c r="N17" t="n">
-        <v>102.2851878561904</v>
+        <v>101.8409335305175</v>
       </c>
       <c r="O17" t="n">
-        <v>10.11361398591969</v>
+        <v>10.09162690206676</v>
       </c>
       <c r="P17" t="n">
-        <v>316.0641736485302</v>
+        <v>316.0981849027151</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -19247,28 +19335,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1609352472761107</v>
+        <v>-0.155182927842295</v>
       </c>
       <c r="J18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K18" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01039007923406798</v>
+        <v>0.009758276192322723</v>
       </c>
       <c r="M18" t="n">
-        <v>10.05052817271272</v>
+        <v>10.04131348572942</v>
       </c>
       <c r="N18" t="n">
-        <v>155.450448410561</v>
+        <v>154.8565956869678</v>
       </c>
       <c r="O18" t="n">
-        <v>12.46797691730944</v>
+        <v>12.44413900946818</v>
       </c>
       <c r="P18" t="n">
-        <v>311.4180563027275</v>
+        <v>311.3631669457608</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19325,28 +19413,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2043640839443917</v>
+        <v>-0.207390129599509</v>
       </c>
       <c r="J19" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K19" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01998832648002591</v>
+        <v>0.02078016927655735</v>
       </c>
       <c r="M19" t="n">
-        <v>8.884490421687898</v>
+        <v>8.85272691509495</v>
       </c>
       <c r="N19" t="n">
-        <v>129.0352641459046</v>
+        <v>128.434291505709</v>
       </c>
       <c r="O19" t="n">
-        <v>11.35936900298184</v>
+        <v>11.33288540071367</v>
       </c>
       <c r="P19" t="n">
-        <v>319.1408804372212</v>
+        <v>319.1697553462162</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19403,28 +19491,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2691119510054168</v>
+        <v>-0.2682697051547647</v>
       </c>
       <c r="J20" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K20" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04249144019523265</v>
+        <v>0.04266969427362854</v>
       </c>
       <c r="M20" t="n">
-        <v>7.580001433609464</v>
+        <v>7.547287927952778</v>
       </c>
       <c r="N20" t="n">
-        <v>102.8375303304599</v>
+        <v>102.3196979484052</v>
       </c>
       <c r="O20" t="n">
-        <v>10.14088410004078</v>
+        <v>10.11531996273006</v>
       </c>
       <c r="P20" t="n">
-        <v>335.3953296893349</v>
+        <v>335.3872928732848</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19481,28 +19569,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3512985402076075</v>
+        <v>-0.3438715554766927</v>
       </c>
       <c r="J21" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K21" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0811907636847099</v>
+        <v>0.07857254423652993</v>
       </c>
       <c r="M21" t="n">
-        <v>7.160106751937273</v>
+        <v>7.15922113455772</v>
       </c>
       <c r="N21" t="n">
-        <v>85.74415182598121</v>
+        <v>85.61848131923318</v>
       </c>
       <c r="O21" t="n">
-        <v>9.259813811626085</v>
+        <v>9.253025522456598</v>
       </c>
       <c r="P21" t="n">
-        <v>362.3800745002997</v>
+        <v>362.3075604628613</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19559,28 +19647,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1099590708108579</v>
+        <v>-0.1079131282413767</v>
       </c>
       <c r="J22" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K22" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01001320502252978</v>
+        <v>0.009747037004517733</v>
       </c>
       <c r="M22" t="n">
-        <v>6.721948848583915</v>
+        <v>6.70095481457485</v>
       </c>
       <c r="N22" t="n">
-        <v>75.32911595393566</v>
+        <v>74.9714325785915</v>
       </c>
       <c r="O22" t="n">
-        <v>8.679234756240648</v>
+        <v>8.658604539912393</v>
       </c>
       <c r="P22" t="n">
-        <v>385.4582465512374</v>
+        <v>385.4387239094019</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -19637,28 +19725,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1768024164482054</v>
+        <v>-0.1746483434841268</v>
       </c>
       <c r="J23" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K23" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02560284338331087</v>
+        <v>0.02525094238634162</v>
       </c>
       <c r="M23" t="n">
-        <v>6.814882138662006</v>
+        <v>6.790719617561313</v>
       </c>
       <c r="N23" t="n">
-        <v>74.96674529250829</v>
+        <v>74.61358097625269</v>
       </c>
       <c r="O23" t="n">
-        <v>8.658333863539122</v>
+        <v>8.637915314255673</v>
       </c>
       <c r="P23" t="n">
-        <v>324.9951822105033</v>
+        <v>324.9746277748156</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -19696,7 +19784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X197"/>
+  <dimension ref="A1:X198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43725,6 +43813,128 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>-34.42686950542999,172.93655545283428</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>-34.42688094300158,172.9374541670904</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>-34.426876420826794,172.9383525320128</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-34.42684665160472,172.9392503437196</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-34.42677585594116,172.9401472557405</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-34.4266965844934,172.94104398109297</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-34.426640662331046,172.94196207713185</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-34.42655394109408,172.9428777350735</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-34.4263962712484,172.9437657172747</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-34.426293199878685,172.94465702275377</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-34.42622824964479,172.9455519256208</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>-34.42619827370745,172.94645012962826</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-34.42620372156249,172.94735167793445</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>-34.42617293630753,172.94824980656347</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>-34.42610708679615,172.94914462511514</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>-34.4260014978493,172.95003569144856</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>-34.425894290556606,172.95092660432476</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>-34.42586166065974,172.95184299606584</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>-34.42558634642158,172.95273804393582</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>-34.42512962641796,172.95354757512155</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>-34.424745770413054,172.95435914547443</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>-34.42511497206985,172.95539185108137</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X198"/>
+  <dimension ref="A1:X200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15892,7 +15892,7 @@
         <v>307.92</v>
       </c>
       <c r="R198" t="n">
-        <v>313.4</v>
+        <v>303.94</v>
       </c>
       <c r="S198" t="n">
         <v>310.43</v>
@@ -15912,6 +15912,162 @@
       <c r="X198" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>278.36</v>
+      </c>
+      <c r="C199" t="n">
+        <v>275.57</v>
+      </c>
+      <c r="D199" t="n">
+        <v>274.55</v>
+      </c>
+      <c r="E199" t="n">
+        <v>276.33</v>
+      </c>
+      <c r="F199" t="n">
+        <v>282.66</v>
+      </c>
+      <c r="G199" t="n">
+        <v>289.93</v>
+      </c>
+      <c r="H199" t="n">
+        <v>294.55</v>
+      </c>
+      <c r="I199" t="n">
+        <v>298.04</v>
+      </c>
+      <c r="J199" t="n">
+        <v>309.12</v>
+      </c>
+      <c r="K199" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="L199" t="n">
+        <v>314.92</v>
+      </c>
+      <c r="M199" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="N199" t="n">
+        <v>304.76</v>
+      </c>
+      <c r="O199" t="n">
+        <v>301.74</v>
+      </c>
+      <c r="P199" t="n">
+        <v>302.62</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="R199" t="n">
+        <v>303.94</v>
+      </c>
+      <c r="S199" t="n">
+        <v>310.43</v>
+      </c>
+      <c r="T199" t="n">
+        <v>329.17</v>
+      </c>
+      <c r="U199" t="n">
+        <v>351.49</v>
+      </c>
+      <c r="V199" t="n">
+        <v>384.76</v>
+      </c>
+      <c r="W199" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>282.37</v>
+      </c>
+      <c r="C200" t="n">
+        <v>280.71</v>
+      </c>
+      <c r="D200" t="n">
+        <v>278.98</v>
+      </c>
+      <c r="E200" t="n">
+        <v>273.75</v>
+      </c>
+      <c r="F200" t="n">
+        <v>279.26</v>
+      </c>
+      <c r="G200" t="n">
+        <v>287.6</v>
+      </c>
+      <c r="H200" t="n">
+        <v>291.87</v>
+      </c>
+      <c r="I200" t="n">
+        <v>295.73</v>
+      </c>
+      <c r="J200" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="K200" t="n">
+        <v>313.98</v>
+      </c>
+      <c r="L200" t="n">
+        <v>317.39</v>
+      </c>
+      <c r="M200" t="n">
+        <v>313.15</v>
+      </c>
+      <c r="N200" t="n">
+        <v>305.76</v>
+      </c>
+      <c r="O200" t="n">
+        <v>304.14</v>
+      </c>
+      <c r="P200" t="n">
+        <v>304.19</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>308.07</v>
+      </c>
+      <c r="R200" t="n">
+        <v>302.78</v>
+      </c>
+      <c r="S200" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="T200" t="n">
+        <v>328.91</v>
+      </c>
+      <c r="U200" t="n">
+        <v>351.82</v>
+      </c>
+      <c r="V200" t="n">
+        <v>382.14</v>
+      </c>
+      <c r="W200" t="n">
+        <v>315.63</v>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -15926,7 +16082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B199"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17919,6 +18075,26 @@
       </c>
       <c r="B199" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -18087,28 +18263,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.026210272101575</v>
+        <v>-1.002188173800739</v>
       </c>
       <c r="J2" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K2" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2255305954773422</v>
+        <v>0.2195834162661694</v>
       </c>
       <c r="M2" t="n">
-        <v>12.37891939442598</v>
+        <v>12.40215250743613</v>
       </c>
       <c r="N2" t="n">
-        <v>229.1633822140338</v>
+        <v>228.6529911566549</v>
       </c>
       <c r="O2" t="n">
-        <v>15.13814328819865</v>
+        <v>15.12127610873682</v>
       </c>
       <c r="P2" t="n">
-        <v>294.2424241190193</v>
+        <v>294.0126598322879</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18165,28 +18341,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8012892307015905</v>
+        <v>-0.7776530165582195</v>
       </c>
       <c r="J3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1873322284724426</v>
+        <v>0.1799791975778925</v>
       </c>
       <c r="M3" t="n">
-        <v>10.90635803715859</v>
+        <v>10.93224972414908</v>
       </c>
       <c r="N3" t="n">
-        <v>176.5033118031297</v>
+        <v>176.4922616542495</v>
       </c>
       <c r="O3" t="n">
-        <v>13.28545489635676</v>
+        <v>13.28503901590994</v>
       </c>
       <c r="P3" t="n">
-        <v>286.256293168131</v>
+        <v>286.0302082261034</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18243,28 +18419,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7529287505765974</v>
+        <v>-0.7274840074031654</v>
       </c>
       <c r="J4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2078680685053571</v>
+        <v>0.1977415226822617</v>
       </c>
       <c r="M4" t="n">
-        <v>9.501000086435781</v>
+        <v>9.563973168179736</v>
       </c>
       <c r="N4" t="n">
-        <v>136.8961426405408</v>
+        <v>137.5354743559068</v>
       </c>
       <c r="O4" t="n">
-        <v>11.70026250306124</v>
+        <v>11.7275519336265</v>
       </c>
       <c r="P4" t="n">
-        <v>282.5810092729604</v>
+        <v>282.3376361287656</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18321,28 +18497,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.526584636427015</v>
+        <v>-0.5109850299953919</v>
       </c>
       <c r="J5" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K5" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L5" t="n">
-        <v>0.127697080775383</v>
+        <v>0.1227018147690159</v>
       </c>
       <c r="M5" t="n">
-        <v>8.634306569990461</v>
+        <v>8.642450313759872</v>
       </c>
       <c r="N5" t="n">
-        <v>120.0318318534704</v>
+        <v>119.5814972911207</v>
       </c>
       <c r="O5" t="n">
-        <v>10.95590397244656</v>
+        <v>10.93533251854376</v>
       </c>
       <c r="P5" t="n">
-        <v>280.3302574303196</v>
+        <v>280.1811018867031</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18399,28 +18575,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4158735117225523</v>
+        <v>-0.398704744949379</v>
       </c>
       <c r="J6" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K6" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09258065655368075</v>
+        <v>0.08669849540678787</v>
       </c>
       <c r="M6" t="n">
-        <v>8.315635187108914</v>
+        <v>8.331811578565695</v>
       </c>
       <c r="N6" t="n">
-        <v>107.41971733154</v>
+        <v>107.2646966029477</v>
       </c>
       <c r="O6" t="n">
-        <v>10.36434837949497</v>
+        <v>10.35686712297439</v>
       </c>
       <c r="P6" t="n">
-        <v>282.4256110069884</v>
+        <v>282.2614573341281</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18477,28 +18653,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3368858359412198</v>
+        <v>-0.3169920472355824</v>
       </c>
       <c r="J7" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K7" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07257505528993469</v>
+        <v>0.06525746021201717</v>
       </c>
       <c r="M7" t="n">
-        <v>7.827886352365412</v>
+        <v>7.870657899427398</v>
       </c>
       <c r="N7" t="n">
-        <v>91.90319513864679</v>
+        <v>92.19555046844069</v>
       </c>
       <c r="O7" t="n">
-        <v>9.586615416227293</v>
+        <v>9.601851408371235</v>
       </c>
       <c r="P7" t="n">
-        <v>286.6139794670877</v>
+        <v>286.4237559877779</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18555,28 +18731,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.339414386077481</v>
+        <v>-0.3281061661067212</v>
       </c>
       <c r="J8" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K8" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0725553577129382</v>
+        <v>0.06917885697004933</v>
       </c>
       <c r="M8" t="n">
-        <v>7.762050441134829</v>
+        <v>7.75031715345667</v>
       </c>
       <c r="N8" t="n">
-        <v>93.31526856212071</v>
+        <v>92.78398681464074</v>
       </c>
       <c r="O8" t="n">
-        <v>9.659982844815032</v>
+        <v>9.632444488012414</v>
       </c>
       <c r="P8" t="n">
-        <v>295.9201576807909</v>
+        <v>295.8120419914106</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18633,28 +18809,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4346984943391409</v>
+        <v>-0.4271034856375681</v>
       </c>
       <c r="J9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L9" t="n">
-        <v>0.11181484123578</v>
+        <v>0.1101983320926871</v>
       </c>
       <c r="M9" t="n">
-        <v>7.777778927752488</v>
+        <v>7.747009993545255</v>
       </c>
       <c r="N9" t="n">
-        <v>95.11610151140177</v>
+        <v>94.34867676209224</v>
       </c>
       <c r="O9" t="n">
-        <v>9.752748408084861</v>
+        <v>9.713324701773963</v>
       </c>
       <c r="P9" t="n">
-        <v>304.201192100522</v>
+        <v>304.1285824794864</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18711,28 +18887,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3730914183599735</v>
+        <v>-0.3615539134480787</v>
       </c>
       <c r="J10" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K10" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0903063896470534</v>
+        <v>0.08655513555409777</v>
       </c>
       <c r="M10" t="n">
-        <v>7.527678211670871</v>
+        <v>7.531785626401761</v>
       </c>
       <c r="N10" t="n">
-        <v>88.85479988259031</v>
+        <v>88.36637078003025</v>
       </c>
       <c r="O10" t="n">
-        <v>9.426282399896065</v>
+        <v>9.400338865170248</v>
       </c>
       <c r="P10" t="n">
-        <v>312.4308660072373</v>
+        <v>312.3205350922171</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18789,28 +18965,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3737349525355302</v>
+        <v>-0.3669246445869216</v>
       </c>
       <c r="J11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0991913488664119</v>
+        <v>0.09762290631033799</v>
       </c>
       <c r="M11" t="n">
-        <v>6.972693545166072</v>
+        <v>6.948079186629966</v>
       </c>
       <c r="N11" t="n">
-        <v>80.38220095493553</v>
+        <v>79.71526276482311</v>
       </c>
       <c r="O11" t="n">
-        <v>8.965612134981946</v>
+        <v>8.928340426127528</v>
       </c>
       <c r="P11" t="n">
-        <v>320.1923192476673</v>
+        <v>320.1271931369456</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18867,28 +19043,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3973509119850668</v>
+        <v>-0.3983493200567923</v>
       </c>
       <c r="J12" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K12" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09944059205953415</v>
+        <v>0.101764412230958</v>
       </c>
       <c r="M12" t="n">
-        <v>7.38109755862357</v>
+        <v>7.318384069316772</v>
       </c>
       <c r="N12" t="n">
-        <v>90.60888867015441</v>
+        <v>89.71682117638281</v>
       </c>
       <c r="O12" t="n">
-        <v>9.518870136216504</v>
+        <v>9.471896387544724</v>
       </c>
       <c r="P12" t="n">
-        <v>327.2833532606479</v>
+        <v>327.292877153646</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18945,28 +19121,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2369131984678494</v>
+        <v>-0.2397840482851828</v>
       </c>
       <c r="J13" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K13" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03154279906264146</v>
+        <v>0.03293685364620513</v>
       </c>
       <c r="M13" t="n">
-        <v>8.105996809147054</v>
+        <v>8.036144811863542</v>
       </c>
       <c r="N13" t="n">
-        <v>109.2024607127622</v>
+        <v>108.1346022813025</v>
       </c>
       <c r="O13" t="n">
-        <v>10.44999812022769</v>
+        <v>10.3987788841432</v>
       </c>
       <c r="P13" t="n">
-        <v>320.3855980400858</v>
+        <v>320.4130391850673</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -19023,28 +19199,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2086158264480809</v>
+        <v>-0.2158150971491616</v>
       </c>
       <c r="J14" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K14" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0242584858998246</v>
+        <v>0.02641223464463538</v>
       </c>
       <c r="M14" t="n">
-        <v>8.317875536204616</v>
+        <v>8.263083241190886</v>
       </c>
       <c r="N14" t="n">
-        <v>110.9275208452598</v>
+        <v>109.9727266009056</v>
       </c>
       <c r="O14" t="n">
-        <v>10.53221348270437</v>
+        <v>10.48678819281221</v>
       </c>
       <c r="P14" t="n">
-        <v>314.8243779243145</v>
+        <v>314.8932153720314</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -19101,28 +19277,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1497401015463972</v>
+        <v>-0.158085692089572</v>
       </c>
       <c r="J15" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K15" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01332799239164806</v>
+        <v>0.01510814008531169</v>
       </c>
       <c r="M15" t="n">
-        <v>7.958979646299882</v>
+        <v>7.907549956927743</v>
       </c>
       <c r="N15" t="n">
-        <v>105.1860210451894</v>
+        <v>104.355192284251</v>
       </c>
       <c r="O15" t="n">
-        <v>10.2560236468716</v>
+        <v>10.21543891784641</v>
       </c>
       <c r="P15" t="n">
-        <v>311.5801963693024</v>
+        <v>311.6599826915902</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -19179,28 +19355,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.174639783812994</v>
+        <v>-0.1847244433066434</v>
       </c>
       <c r="J16" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K16" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01648616824732629</v>
+        <v>0.01873925437846247</v>
       </c>
       <c r="M16" t="n">
-        <v>8.238705795454331</v>
+        <v>8.192383113759332</v>
       </c>
       <c r="N16" t="n">
-        <v>115.2977477772608</v>
+        <v>114.4543332497295</v>
       </c>
       <c r="O16" t="n">
-        <v>10.73767888220079</v>
+        <v>10.69833319960308</v>
       </c>
       <c r="P16" t="n">
-        <v>313.6804019204793</v>
+        <v>313.7768270309082</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -19257,28 +19433,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1644518859493033</v>
+        <v>-0.1711370003610226</v>
       </c>
       <c r="J17" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K17" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01654937567996928</v>
+        <v>0.01824410765923656</v>
       </c>
       <c r="M17" t="n">
-        <v>7.946546868698226</v>
+        <v>7.891557901928324</v>
       </c>
       <c r="N17" t="n">
-        <v>101.8409335305175</v>
+        <v>100.9532045035076</v>
       </c>
       <c r="O17" t="n">
-        <v>10.09162690206676</v>
+        <v>10.04754718841905</v>
       </c>
       <c r="P17" t="n">
-        <v>316.0981849027151</v>
+        <v>316.1621137046808</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -19335,28 +19511,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.155182927842295</v>
+        <v>-0.1705639662129199</v>
       </c>
       <c r="J18" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K18" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L18" t="n">
-        <v>0.009758276192322723</v>
+        <v>0.01201008769271361</v>
       </c>
       <c r="M18" t="n">
-        <v>10.04131348572942</v>
+        <v>9.933120542573858</v>
       </c>
       <c r="N18" t="n">
-        <v>154.8565956869678</v>
+        <v>153.2965187314661</v>
       </c>
       <c r="O18" t="n">
-        <v>12.44413900946818</v>
+        <v>12.38129713444702</v>
       </c>
       <c r="P18" t="n">
-        <v>311.3631669457608</v>
+        <v>311.5100857850003</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19413,28 +19589,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.207390129599509</v>
+        <v>-0.2137812814025636</v>
       </c>
       <c r="J19" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K19" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02078016927655735</v>
+        <v>0.02248499503766288</v>
       </c>
       <c r="M19" t="n">
-        <v>8.85272691509495</v>
+        <v>8.791512624121918</v>
       </c>
       <c r="N19" t="n">
-        <v>128.434291505709</v>
+        <v>127.2686320718666</v>
       </c>
       <c r="O19" t="n">
-        <v>11.33288540071367</v>
+        <v>11.28133999451602</v>
       </c>
       <c r="P19" t="n">
-        <v>319.1697553462162</v>
+        <v>319.2308809012076</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19491,28 +19667,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2682697051547647</v>
+        <v>-0.2668674941125694</v>
       </c>
       <c r="J20" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K20" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04266969427362854</v>
+        <v>0.04309367116673868</v>
       </c>
       <c r="M20" t="n">
-        <v>7.547287927952778</v>
+        <v>7.480905662246873</v>
       </c>
       <c r="N20" t="n">
-        <v>102.3196979484052</v>
+        <v>101.2974882126864</v>
       </c>
       <c r="O20" t="n">
-        <v>10.11531996273006</v>
+        <v>10.06466533038662</v>
       </c>
       <c r="P20" t="n">
-        <v>335.3872928732848</v>
+        <v>335.3738858033354</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19569,28 +19745,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3438715554766927</v>
+        <v>-0.3466387621967293</v>
       </c>
       <c r="J21" t="n">
+        <v>199</v>
+      </c>
+      <c r="K21" t="n">
         <v>197</v>
       </c>
-      <c r="K21" t="n">
-        <v>195</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.07857254423652993</v>
+        <v>0.08128086054342543</v>
       </c>
       <c r="M21" t="n">
-        <v>7.15922113455772</v>
+        <v>7.103107080147229</v>
       </c>
       <c r="N21" t="n">
-        <v>85.61848131923318</v>
+        <v>84.77201045960668</v>
       </c>
       <c r="O21" t="n">
-        <v>9.253025522456598</v>
+        <v>9.207171686224097</v>
       </c>
       <c r="P21" t="n">
-        <v>362.3075604628613</v>
+        <v>362.3346329793389</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19647,28 +19823,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1079131282413767</v>
+        <v>-0.1063361327370216</v>
       </c>
       <c r="J22" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K22" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009747037004517733</v>
+        <v>0.009661460959984991</v>
       </c>
       <c r="M22" t="n">
-        <v>6.70095481457485</v>
+        <v>6.648159485043149</v>
       </c>
       <c r="N22" t="n">
-        <v>74.9714325785915</v>
+        <v>74.24273937927168</v>
       </c>
       <c r="O22" t="n">
-        <v>8.658604539912393</v>
+        <v>8.616422655561395</v>
       </c>
       <c r="P22" t="n">
-        <v>385.4387239094019</v>
+        <v>385.4236681958237</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -19725,28 +19901,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1746483434841268</v>
+        <v>-0.1834507069489691</v>
       </c>
       <c r="J23" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K23" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02525094238634162</v>
+        <v>0.02826965351509703</v>
       </c>
       <c r="M23" t="n">
-        <v>6.790719617561313</v>
+        <v>6.777104322290692</v>
       </c>
       <c r="N23" t="n">
-        <v>74.61358097625269</v>
+        <v>74.09952897014075</v>
       </c>
       <c r="O23" t="n">
-        <v>8.637915314255673</v>
+        <v>8.608108327044958</v>
       </c>
       <c r="P23" t="n">
-        <v>324.9746277748156</v>
+        <v>325.0588012741594</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -19784,7 +19960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X198"/>
+  <dimension ref="A1:X200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43901,7 +44077,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>-34.425894290556606,172.95092660432476</t>
+          <t>-34.42597934363031,172.9509346354352</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
@@ -43932,6 +44108,250 @@
       <c r="X198" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>-34.42686950542999,172.93655545283428</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>-34.42688094300158,172.9374541670904</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-34.426876420826794,172.9383525320128</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-34.42684665160472,172.9392503437196</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-34.42677585594116,172.9401472557405</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-34.4266965844934,172.94104398109297</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-34.426640662331046,172.94196207713185</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-34.42655394109408,172.9428777350735</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-34.4263962712484,172.9437657172747</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-34.426293199878685,172.94465702275377</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-34.42622824964479,172.9455519256208</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>-34.42619827370745,172.94645012962826</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>-34.42620372156249,172.94735167793445</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>-34.42617293630753,172.94824980656347</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>-34.42610708679615,172.94914462511514</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>-34.4260014978493,172.95003569144856</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>-34.42597934363031,172.9509346354352</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>-34.42586166065974,172.95184299606584</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>-34.42558634642158,172.95273804393582</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>-34.425212433164255,172.95357189053365</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>-34.424745770413054,172.95435914547443</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>-34.42518016576243,172.95541099558915</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>-34.42683334804703,172.93655466111855</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>-34.42683459663475,172.93745315195213</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>-34.42683647639369,172.93835165682177</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-34.426869914951844,172.9392508535854</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-34.42680651306281,172.9401479278676</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-34.426717593636866,172.94104444184208</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-34.42666480624313,172.94196340611845</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-34.42657471397407,172.94287963171394</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-34.42639932813466,172.94376600575225</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-34.42629463841279,172.9446571585176</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-34.42620604228387,172.94554982961589</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>-34.426186225994634,172.94644899244125</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>-34.426194730736,172.94735082922477</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>-34.426151358333286,172.94824776951188</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>-34.426092971210686,172.94914329244764</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>-34.42600014922704,172.95003556411453</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>-34.42598977297114,172.95093562022365</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>-34.425867756480095,172.95184380359822</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>-34.42558864908926,172.9527385776612</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>-34.42520954150019,172.9535710414232</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>-34.424768728448406,172.9543658869923</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>-34.425176397847494,172.95540988911816</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0002/nzd0002.xlsx
+++ b/data/nzd0002/nzd0002.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X200"/>
+  <dimension ref="A1:X201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16066,6 +16066,84 @@
         <v>315.63</v>
       </c>
       <c r="X200" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>283.15</v>
+      </c>
+      <c r="C201" t="n">
+        <v>278.59</v>
+      </c>
+      <c r="D201" t="n">
+        <v>275.98</v>
+      </c>
+      <c r="E201" t="n">
+        <v>268.64</v>
+      </c>
+      <c r="F201" t="n">
+        <v>274.1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>281.03</v>
+      </c>
+      <c r="H201" t="n">
+        <v>285.35</v>
+      </c>
+      <c r="I201" t="n">
+        <v>290.75</v>
+      </c>
+      <c r="J201" t="n">
+        <v>305.44</v>
+      </c>
+      <c r="K201" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="L201" t="n">
+        <v>315.12</v>
+      </c>
+      <c r="M201" t="n">
+        <v>311.48</v>
+      </c>
+      <c r="N201" t="n">
+        <v>303.7</v>
+      </c>
+      <c r="O201" t="n">
+        <v>302</v>
+      </c>
+      <c r="P201" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>304.1</v>
+      </c>
+      <c r="R201" t="n">
+        <v>298.6</v>
+      </c>
+      <c r="S201" t="n">
+        <v>306.88</v>
+      </c>
+      <c r="T201" t="n">
+        <v>326.62</v>
+      </c>
+      <c r="U201" t="n">
+        <v>348.91</v>
+      </c>
+      <c r="V201" t="n">
+        <v>378.33</v>
+      </c>
+      <c r="W201" t="n">
+        <v>314.98</v>
+      </c>
+      <c r="X201" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16082,7 +16160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:B202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18095,6 +18173,16 @@
       </c>
       <c r="B201" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -18263,28 +18351,28 @@
         <v>0.0553</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.002188173800739</v>
+        <v>-0.9880346496950081</v>
       </c>
       <c r="J2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K2" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2195834162661694</v>
+        <v>0.2155685741711879</v>
       </c>
       <c r="M2" t="n">
-        <v>12.40215250743613</v>
+        <v>12.42759460428644</v>
       </c>
       <c r="N2" t="n">
-        <v>228.6529911566549</v>
+        <v>228.7538101846816</v>
       </c>
       <c r="O2" t="n">
-        <v>15.12127610873682</v>
+        <v>15.12460942254978</v>
       </c>
       <c r="P2" t="n">
-        <v>294.0126598322879</v>
+        <v>293.8765539593145</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18341,28 +18429,28 @@
         <v>0.0498</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7776530165582195</v>
+        <v>-0.7657883506366594</v>
       </c>
       <c r="J3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1799791975778925</v>
+        <v>0.1762609727450322</v>
       </c>
       <c r="M3" t="n">
-        <v>10.93224972414908</v>
+        <v>10.94468376689827</v>
       </c>
       <c r="N3" t="n">
-        <v>176.4922616542495</v>
+        <v>176.4840421096364</v>
       </c>
       <c r="O3" t="n">
-        <v>13.28503901590994</v>
+        <v>13.28472965888416</v>
       </c>
       <c r="P3" t="n">
-        <v>286.0302082261034</v>
+        <v>285.9161129166436</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18419,28 +18507,28 @@
         <v>0.0504</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7274840074031654</v>
+        <v>-0.7158516674119086</v>
       </c>
       <c r="J4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1977415226822617</v>
+        <v>0.193330239257014</v>
       </c>
       <c r="M4" t="n">
-        <v>9.563973168179736</v>
+        <v>9.590796713905041</v>
       </c>
       <c r="N4" t="n">
-        <v>137.5354743559068</v>
+        <v>137.6881363252523</v>
       </c>
       <c r="O4" t="n">
-        <v>11.7275519336265</v>
+        <v>11.73405881718906</v>
       </c>
       <c r="P4" t="n">
-        <v>282.3376361287656</v>
+        <v>282.2257749571305</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18497,28 +18585,28 @@
         <v>0.0571</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5109850299953919</v>
+        <v>-0.5091098408232035</v>
       </c>
       <c r="J5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K5" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1227018147690159</v>
+        <v>0.1230012784793575</v>
       </c>
       <c r="M5" t="n">
-        <v>8.642450313759872</v>
+        <v>8.610832262945992</v>
       </c>
       <c r="N5" t="n">
-        <v>119.5814972911207</v>
+        <v>119.0054276956912</v>
       </c>
       <c r="O5" t="n">
-        <v>10.93533251854376</v>
+        <v>10.90896088982315</v>
       </c>
       <c r="P5" t="n">
-        <v>280.1811018867031</v>
+        <v>280.1630693276483</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18575,28 +18663,28 @@
         <v>0.067</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.398704744949379</v>
+        <v>-0.3964895792144439</v>
       </c>
       <c r="J6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K6" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08669849540678787</v>
+        <v>0.08661042691609344</v>
       </c>
       <c r="M6" t="n">
-        <v>8.331811578565695</v>
+        <v>8.302991358962476</v>
       </c>
       <c r="N6" t="n">
-        <v>107.2646966029477</v>
+        <v>106.7588473660813</v>
       </c>
       <c r="O6" t="n">
-        <v>10.35686712297439</v>
+        <v>10.33241730506861</v>
       </c>
       <c r="P6" t="n">
-        <v>282.2614573341281</v>
+        <v>282.2401554262864</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18653,28 +18741,28 @@
         <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3169920472355824</v>
+        <v>-0.3142550835060958</v>
       </c>
       <c r="J7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06525746021201717</v>
+        <v>0.06479934882586513</v>
       </c>
       <c r="M7" t="n">
-        <v>7.870657899427398</v>
+        <v>7.847815386468813</v>
       </c>
       <c r="N7" t="n">
-        <v>92.19555046844069</v>
+        <v>91.78109474058068</v>
       </c>
       <c r="O7" t="n">
-        <v>9.601851408371235</v>
+        <v>9.580245025080552</v>
       </c>
       <c r="P7" t="n">
-        <v>286.4237559877779</v>
+        <v>286.3974362645121</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18731,28 +18819,28 @@
         <v>0.0736</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3281061661067212</v>
+        <v>-0.3296196752906442</v>
       </c>
       <c r="J8" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K8" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06917885697004933</v>
+        <v>0.07043634495942952</v>
       </c>
       <c r="M8" t="n">
-        <v>7.75031715345667</v>
+        <v>7.719481742882472</v>
       </c>
       <c r="N8" t="n">
-        <v>92.78398681464074</v>
+        <v>92.33429313731733</v>
       </c>
       <c r="O8" t="n">
-        <v>9.632444488012414</v>
+        <v>9.609073479650228</v>
       </c>
       <c r="P8" t="n">
-        <v>295.8120419914106</v>
+        <v>295.8265964929745</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18809,28 +18897,28 @@
         <v>0.0733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4271034856375681</v>
+        <v>-0.4288586195075283</v>
       </c>
       <c r="J9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1101983320926871</v>
+        <v>0.1120069369563941</v>
       </c>
       <c r="M9" t="n">
-        <v>7.747009993545255</v>
+        <v>7.716897028230028</v>
       </c>
       <c r="N9" t="n">
-        <v>94.34867676209224</v>
+        <v>93.89606452558179</v>
       </c>
       <c r="O9" t="n">
-        <v>9.713324701773963</v>
+        <v>9.689998169534491</v>
       </c>
       <c r="P9" t="n">
-        <v>304.1285824794864</v>
+        <v>304.1454605393796</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18887,28 +18975,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3615539134480787</v>
+        <v>-0.3590849657705813</v>
       </c>
       <c r="J10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K10" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08655513555409777</v>
+        <v>0.0862536535476669</v>
       </c>
       <c r="M10" t="n">
-        <v>7.531785626401761</v>
+        <v>7.510956504134855</v>
       </c>
       <c r="N10" t="n">
-        <v>88.36637078003025</v>
+        <v>87.96239576041229</v>
       </c>
       <c r="O10" t="n">
-        <v>9.400338865170248</v>
+        <v>9.378826992775391</v>
       </c>
       <c r="P10" t="n">
-        <v>312.3205350922171</v>
+        <v>312.2967927170701</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18965,28 +19053,28 @@
         <v>0.0668</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3669246445869216</v>
+        <v>-0.3671779529030338</v>
       </c>
       <c r="J11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09762290631033799</v>
+        <v>0.09865763148437845</v>
       </c>
       <c r="M11" t="n">
-        <v>6.948079186629966</v>
+        <v>6.914471758445386</v>
       </c>
       <c r="N11" t="n">
-        <v>79.71526276482311</v>
+        <v>79.31708494282466</v>
       </c>
       <c r="O11" t="n">
-        <v>8.928340426127528</v>
+        <v>8.906013976118871</v>
       </c>
       <c r="P11" t="n">
-        <v>320.1271931369456</v>
+        <v>320.1296290496722</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -19043,28 +19131,28 @@
         <v>0.0537</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3983493200567923</v>
+        <v>-0.3997144639661322</v>
       </c>
       <c r="J12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>0.101764412230958</v>
+        <v>0.1033315205776085</v>
       </c>
       <c r="M12" t="n">
-        <v>7.318384069316772</v>
+        <v>7.287961055077959</v>
       </c>
       <c r="N12" t="n">
-        <v>89.71682117638281</v>
+        <v>89.27981090833087</v>
       </c>
       <c r="O12" t="n">
-        <v>9.471896387544724</v>
+        <v>9.448799442698045</v>
       </c>
       <c r="P12" t="n">
-        <v>327.292877153646</v>
+        <v>327.3060049161825</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -19121,28 +19209,28 @@
         <v>0.0733</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2397840482851828</v>
+        <v>-0.2420358563936245</v>
       </c>
       <c r="J13" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K13" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03293685364620513</v>
+        <v>0.03386392616331779</v>
       </c>
       <c r="M13" t="n">
-        <v>8.036144811863542</v>
+        <v>8.004925017107245</v>
       </c>
       <c r="N13" t="n">
-        <v>108.1346022813025</v>
+        <v>107.6254200397897</v>
       </c>
       <c r="O13" t="n">
-        <v>10.3987788841432</v>
+        <v>10.37426720495427</v>
       </c>
       <c r="P13" t="n">
-        <v>320.4130391850673</v>
+        <v>320.4346934604321</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -19199,28 +19287,28 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2158150971491616</v>
+        <v>-0.220649252317598</v>
       </c>
       <c r="J14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02641223464463538</v>
+        <v>0.02781783386717729</v>
       </c>
       <c r="M14" t="n">
-        <v>8.263083241190886</v>
+        <v>8.241322298132363</v>
       </c>
       <c r="N14" t="n">
-        <v>109.9727266009056</v>
+        <v>109.5679944713057</v>
       </c>
       <c r="O14" t="n">
-        <v>10.48678819281221</v>
+        <v>10.46747316554027</v>
       </c>
       <c r="P14" t="n">
-        <v>314.8932153720314</v>
+        <v>314.9397025157542</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -19277,28 +19365,28 @@
         <v>0.082</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.158085692089572</v>
+        <v>-0.1629306345304505</v>
       </c>
       <c r="J15" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K15" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01510814008531169</v>
+        <v>0.01617452577641554</v>
       </c>
       <c r="M15" t="n">
-        <v>7.907549956927743</v>
+        <v>7.884819879792623</v>
       </c>
       <c r="N15" t="n">
-        <v>104.355192284251</v>
+        <v>103.9791962621151</v>
       </c>
       <c r="O15" t="n">
-        <v>10.21543891784641</v>
+        <v>10.19701898900434</v>
       </c>
       <c r="P15" t="n">
-        <v>311.6599826915902</v>
+        <v>311.7065735699817</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -19355,28 +19443,28 @@
         <v>0.1136</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1847244433066434</v>
+        <v>-0.1914407005617603</v>
       </c>
       <c r="J16" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K16" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01873925437846247</v>
+        <v>0.02025415347141091</v>
       </c>
       <c r="M16" t="n">
-        <v>8.192383113759332</v>
+        <v>8.175472060377523</v>
       </c>
       <c r="N16" t="n">
-        <v>114.4543332497295</v>
+        <v>114.1622016108</v>
       </c>
       <c r="O16" t="n">
-        <v>10.69833319960308</v>
+        <v>10.68467133845492</v>
       </c>
       <c r="P16" t="n">
-        <v>313.7768270309082</v>
+        <v>313.8414132109997</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -19433,28 +19521,28 @@
         <v>0.0735</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1711370003610226</v>
+        <v>-0.1778087942540734</v>
       </c>
       <c r="J17" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K17" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01824410765923656</v>
+        <v>0.01981223348598682</v>
       </c>
       <c r="M17" t="n">
-        <v>7.891557901928324</v>
+        <v>7.87650577833441</v>
       </c>
       <c r="N17" t="n">
-        <v>100.9532045035076</v>
+        <v>100.7248815872034</v>
       </c>
       <c r="O17" t="n">
-        <v>10.04754718841905</v>
+        <v>10.03617863467981</v>
       </c>
       <c r="P17" t="n">
-        <v>316.1621137046808</v>
+        <v>316.2262723075368</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -19511,28 +19599,28 @@
         <v>0.064</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1705639662129199</v>
+        <v>-0.1780026562023187</v>
       </c>
       <c r="J18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01201008769271361</v>
+        <v>0.01317093535826575</v>
       </c>
       <c r="M18" t="n">
-        <v>9.933120542573858</v>
+        <v>9.909289819621394</v>
       </c>
       <c r="N18" t="n">
-        <v>153.2965187314661</v>
+        <v>152.8736838370355</v>
       </c>
       <c r="O18" t="n">
-        <v>12.38129713444702</v>
+        <v>12.36420979428267</v>
       </c>
       <c r="P18" t="n">
-        <v>311.5100857850003</v>
+        <v>311.5816191633464</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -19589,28 +19677,28 @@
         <v>0.0745</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2137812814025636</v>
+        <v>-0.2196963809002821</v>
       </c>
       <c r="J19" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K19" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02248499503766288</v>
+        <v>0.02391653040296704</v>
       </c>
       <c r="M19" t="n">
-        <v>8.791512624121918</v>
+        <v>8.772844616559507</v>
       </c>
       <c r="N19" t="n">
-        <v>127.2686320718666</v>
+        <v>126.849581358066</v>
       </c>
       <c r="O19" t="n">
-        <v>11.28133999451602</v>
+        <v>11.26275194426593</v>
       </c>
       <c r="P19" t="n">
-        <v>319.2308809012076</v>
+        <v>319.2877628321561</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -19667,28 +19755,28 @@
         <v>0.0929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2668674941125694</v>
+        <v>-0.2683154566118978</v>
       </c>
       <c r="J20" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04309367116673868</v>
+        <v>0.04396835751514416</v>
       </c>
       <c r="M20" t="n">
-        <v>7.480905662246873</v>
+        <v>7.449871363383188</v>
       </c>
       <c r="N20" t="n">
-        <v>101.2974882126864</v>
+        <v>100.8040214961164</v>
       </c>
       <c r="O20" t="n">
-        <v>10.06466533038662</v>
+        <v>10.04012059171185</v>
       </c>
       <c r="P20" t="n">
-        <v>335.3738858033354</v>
+        <v>335.3878099821146</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -19745,28 +19833,28 @@
         <v>0.0733</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3466387621967293</v>
+        <v>-0.3504347966349726</v>
       </c>
       <c r="J21" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08128086054342543</v>
+        <v>0.08363922411199687</v>
       </c>
       <c r="M21" t="n">
-        <v>7.103107080147229</v>
+        <v>7.089643442788771</v>
       </c>
       <c r="N21" t="n">
-        <v>84.77201045960668</v>
+        <v>84.43025499259933</v>
       </c>
       <c r="O21" t="n">
-        <v>9.207171686224097</v>
+        <v>9.188593744017597</v>
       </c>
       <c r="P21" t="n">
-        <v>362.3346329793389</v>
+        <v>362.3719780228172</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -19823,28 +19911,28 @@
         <v>0.0495</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1063361327370216</v>
+        <v>-0.1101209145461433</v>
       </c>
       <c r="J22" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L22" t="n">
-        <v>0.009661460959984991</v>
+        <v>0.01044799437737076</v>
       </c>
       <c r="M22" t="n">
-        <v>6.648159485043149</v>
+        <v>6.632527479128568</v>
       </c>
       <c r="N22" t="n">
-        <v>74.24273937927168</v>
+        <v>73.96048720686835</v>
       </c>
       <c r="O22" t="n">
-        <v>8.616422655561395</v>
+        <v>8.600028325934069</v>
       </c>
       <c r="P22" t="n">
-        <v>385.4236681958237</v>
+        <v>385.4600641512265</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -19901,28 +19989,28 @@
         <v>0.0799</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1834507069489691</v>
+        <v>-0.1880593176686774</v>
       </c>
       <c r="J23" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K23" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02826965351509703</v>
+        <v>0.02991166832469827</v>
       </c>
       <c r="M23" t="n">
-        <v>6.777104322290692</v>
+        <v>6.771566943477717</v>
       </c>
       <c r="N23" t="n">
-        <v>74.09952897014075</v>
+        <v>73.8609361170351</v>
       </c>
       <c r="O23" t="n">
-        <v>8.608108327044958</v>
+        <v>8.594238542013777</v>
       </c>
       <c r="P23" t="n">
-        <v>325.0588012741594</v>
+        <v>325.1031194934604</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -19960,7 +20048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X200"/>
+  <dimension ref="A1:X201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44355,6 +44443,128 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>-34.4268263149401,172.93655450711907</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>-34.42685371225691,172.93745357064714</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-34.426863526799885,172.93835224950186</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-34.42691599080581,172.9392518634367</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-34.42685303975299,172.94014894792022</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-34.42677683401096,172.94104574103716</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-34.42672354441685,172.9419666393278</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-34.426619497065644,172.9428837205783</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-34.42642935754654,172.94376883962153</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-34.42632997240666,172.94466049321827</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-34.42622645147792,172.94555175590375</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-34.4262012406815,172.94645040968183</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-34.426213251838554,172.94735257756693</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-34.42617059869366,172.94824958588285</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>-34.42611895467688,172.94914574557478</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>-34.42603584276248,172.95003893422248</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>-34.426027354561214,172.95093916885986</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>-34.425893484427604,172.95184721186132</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>-34.42560893027759,172.95274327855125</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>-34.42523504071934,172.95357852903547</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>-34.42480211398756,172.9543756905038</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>-34.42518209353285,172.95541156169065</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
